--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72251A57-3E23-FE45-BEBC-6963C635BC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BB749C-00FB-324E-9985-6C425A9E5621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
